--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4semestre\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37D53EC-5DC2-4FEB-9010-EA794BBFDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C9C8A-4C30-4DCE-BB11-E46BA7CF22ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1231,8 +1231,12 @@
       <c r="BG1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
+      <c r="BH1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1440,8 +1444,12 @@
       <c r="BG2" s="1">
         <v>46276</v>
       </c>
-      <c r="BH2" s="1"/>
-      <c r="BI2" s="1"/>
+      <c r="BH2" s="1">
+        <v>46281</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>46283</v>
+      </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1649,6 +1657,12 @@
         <v>36</v>
       </c>
       <c r="BG3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1880,6 +1894,12 @@
       <c r="BG4" t="s">
         <v>36</v>
       </c>
+      <c r="BH4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2109,6 +2129,12 @@
       <c r="BG5" t="s">
         <v>37</v>
       </c>
+      <c r="BH5" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2338,6 +2364,12 @@
       <c r="BG6" t="s">
         <v>36</v>
       </c>
+      <c r="BH6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2553,6 +2585,12 @@
       <c r="BG7" t="s">
         <v>36</v>
       </c>
+      <c r="BH7" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2768,6 +2806,12 @@
       <c r="BG8" t="s">
         <v>37</v>
       </c>
+      <c r="BH8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2983,6 +3027,12 @@
       <c r="BG9" t="s">
         <v>36</v>
       </c>
+      <c r="BH9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3198,6 +3248,12 @@
       <c r="BG10" t="s">
         <v>36</v>
       </c>
+      <c r="BH10" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3413,6 +3469,12 @@
       <c r="BG11" t="s">
         <v>36</v>
       </c>
+      <c r="BH11" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3628,6 +3690,12 @@
       <c r="BG12" t="s">
         <v>36</v>
       </c>
+      <c r="BH12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3843,6 +3911,12 @@
       <c r="BG13" t="s">
         <v>36</v>
       </c>
+      <c r="BH13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4058,6 +4132,12 @@
       <c r="BG14" t="s">
         <v>38</v>
       </c>
+      <c r="BH14" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4273,6 +4353,12 @@
       <c r="BG15" t="s">
         <v>36</v>
       </c>
+      <c r="BH15" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4488,6 +4574,12 @@
       <c r="BG16" t="s">
         <v>36</v>
       </c>
+      <c r="BH16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4703,6 +4795,12 @@
       <c r="BG17" t="s">
         <v>36</v>
       </c>
+      <c r="BH17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4918,6 +5016,12 @@
       <c r="BG18" t="s">
         <v>36</v>
       </c>
+      <c r="BH18" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5133,6 +5237,12 @@
       <c r="BG19" t="s">
         <v>36</v>
       </c>
+      <c r="BH19" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5348,6 +5458,12 @@
       <c r="BG20" t="s">
         <v>36</v>
       </c>
+      <c r="BH20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5563,6 +5679,12 @@
       <c r="BG21" t="s">
         <v>36</v>
       </c>
+      <c r="BH21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5778,6 +5900,12 @@
       <c r="BG22" t="s">
         <v>36</v>
       </c>
+      <c r="BH22" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5993,6 +6121,12 @@
       <c r="BG23" t="s">
         <v>36</v>
       </c>
+      <c r="BH23" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6208,6 +6342,12 @@
       <c r="BG24" t="s">
         <v>36</v>
       </c>
+      <c r="BH24" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6423,6 +6563,12 @@
       <c r="BG25" t="s">
         <v>36</v>
       </c>
+      <c r="BH25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6638,6 +6784,12 @@
       <c r="BG26" t="s">
         <v>36</v>
       </c>
+      <c r="BH26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6853,6 +7005,12 @@
       <c r="BG27" t="s">
         <v>36</v>
       </c>
+      <c r="BH27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7068,6 +7226,12 @@
       <c r="BG28" t="s">
         <v>36</v>
       </c>
+      <c r="BH28" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7283,6 +7447,12 @@
       <c r="BG29" t="s">
         <v>36</v>
       </c>
+      <c r="BH29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7498,6 +7668,12 @@
       <c r="BG30" t="s">
         <v>36</v>
       </c>
+      <c r="BH30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7713,6 +7889,12 @@
       <c r="BG31" t="s">
         <v>37</v>
       </c>
+      <c r="BH31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7928,6 +8110,12 @@
       <c r="BG32" t="s">
         <v>36</v>
       </c>
+      <c r="BH32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8141,6 +8329,12 @@
         <v>46</v>
       </c>
       <c r="BG33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BI33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4semestre\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C9C8A-4C30-4DCE-BB11-E46BA7CF22ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A40F59C-0830-498B-B9B6-20325C81B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1237,8 +1237,12 @@
       <c r="BI1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
+      <c r="BJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
@@ -1450,8 +1454,12 @@
       <c r="BI2" s="1">
         <v>46283</v>
       </c>
-      <c r="BJ2" s="1"/>
-      <c r="BK2" s="1"/>
+      <c r="BJ2" s="1">
+        <v>46288</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>46290</v>
+      </c>
       <c r="BL2" s="1"/>
       <c r="BM2" s="1"/>
       <c r="BN2" s="1"/>
@@ -1663,6 +1671,9 @@
         <v>36</v>
       </c>
       <c r="BI3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1900,6 +1911,9 @@
       <c r="BI4" t="s">
         <v>36</v>
       </c>
+      <c r="BJ4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2135,6 +2149,9 @@
       <c r="BI5" t="s">
         <v>36</v>
       </c>
+      <c r="BJ5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2370,6 +2387,9 @@
       <c r="BI6" t="s">
         <v>36</v>
       </c>
+      <c r="BJ6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2591,6 +2611,9 @@
       <c r="BI7" t="s">
         <v>36</v>
       </c>
+      <c r="BJ7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2812,6 +2835,9 @@
       <c r="BI8" t="s">
         <v>37</v>
       </c>
+      <c r="BJ8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3033,6 +3059,9 @@
       <c r="BI9" t="s">
         <v>36</v>
       </c>
+      <c r="BJ9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3254,6 +3283,9 @@
       <c r="BI10" t="s">
         <v>36</v>
       </c>
+      <c r="BJ10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3475,6 +3507,9 @@
       <c r="BI11" t="s">
         <v>36</v>
       </c>
+      <c r="BJ11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3696,6 +3731,9 @@
       <c r="BI12" t="s">
         <v>36</v>
       </c>
+      <c r="BJ12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3917,6 +3955,9 @@
       <c r="BI13" t="s">
         <v>36</v>
       </c>
+      <c r="BJ13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4138,6 +4179,9 @@
       <c r="BI14" t="s">
         <v>37</v>
       </c>
+      <c r="BJ14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4359,6 +4403,9 @@
       <c r="BI15" t="s">
         <v>36</v>
       </c>
+      <c r="BJ15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4580,6 +4627,9 @@
       <c r="BI16" t="s">
         <v>36</v>
       </c>
+      <c r="BJ16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4801,6 +4851,9 @@
       <c r="BI17" t="s">
         <v>36</v>
       </c>
+      <c r="BJ17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5022,6 +5075,9 @@
       <c r="BI18" t="s">
         <v>36</v>
       </c>
+      <c r="BJ18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5243,6 +5299,9 @@
       <c r="BI19" t="s">
         <v>36</v>
       </c>
+      <c r="BJ19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5464,6 +5523,9 @@
       <c r="BI20" t="s">
         <v>36</v>
       </c>
+      <c r="BJ20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5685,6 +5747,9 @@
       <c r="BI21" t="s">
         <v>36</v>
       </c>
+      <c r="BJ21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5906,6 +5971,9 @@
       <c r="BI22" t="s">
         <v>36</v>
       </c>
+      <c r="BJ22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6127,6 +6195,9 @@
       <c r="BI23" t="s">
         <v>36</v>
       </c>
+      <c r="BJ23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6348,6 +6419,9 @@
       <c r="BI24" t="s">
         <v>36</v>
       </c>
+      <c r="BJ24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6569,6 +6643,9 @@
       <c r="BI25" t="s">
         <v>36</v>
       </c>
+      <c r="BJ25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6790,6 +6867,9 @@
       <c r="BI26" t="s">
         <v>36</v>
       </c>
+      <c r="BJ26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7011,6 +7091,9 @@
       <c r="BI27" t="s">
         <v>36</v>
       </c>
+      <c r="BJ27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7232,6 +7315,9 @@
       <c r="BI28" t="s">
         <v>36</v>
       </c>
+      <c r="BJ28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7453,6 +7539,9 @@
       <c r="BI29" t="s">
         <v>36</v>
       </c>
+      <c r="BJ29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7674,6 +7763,9 @@
       <c r="BI30" t="s">
         <v>36</v>
       </c>
+      <c r="BJ30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7895,6 +7987,9 @@
       <c r="BI31" t="s">
         <v>36</v>
       </c>
+      <c r="BJ31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8116,6 +8211,9 @@
       <c r="BI32" t="s">
         <v>36</v>
       </c>
+      <c r="BJ32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8335,6 +8433,9 @@
         <v>36</v>
       </c>
       <c r="BI33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A40F59C-0830-498B-B9B6-20325C81B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEF2BC2-3459-42A7-AD8B-06E1649DF71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1243,8 +1243,12 @@
       <c r="BK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
+      <c r="BL1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
@@ -1460,8 +1464,12 @@
       <c r="BK2" s="1">
         <v>46290</v>
       </c>
-      <c r="BL2" s="1"/>
-      <c r="BM2" s="1"/>
+      <c r="BL2" s="1">
+        <v>46295</v>
+      </c>
+      <c r="BM2" s="1">
+        <v>46297</v>
+      </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1"/>
       <c r="BP2" s="1"/>
@@ -1674,6 +1682,12 @@
         <v>36</v>
       </c>
       <c r="BJ3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1914,6 +1928,12 @@
       <c r="BJ4" t="s">
         <v>36</v>
       </c>
+      <c r="BK4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2152,6 +2172,12 @@
       <c r="BJ5" t="s">
         <v>36</v>
       </c>
+      <c r="BK5" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2390,6 +2416,12 @@
       <c r="BJ6" t="s">
         <v>36</v>
       </c>
+      <c r="BK6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2614,6 +2646,12 @@
       <c r="BJ7" t="s">
         <v>36</v>
       </c>
+      <c r="BK7" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2838,6 +2876,12 @@
       <c r="BJ8" t="s">
         <v>36</v>
       </c>
+      <c r="BK8" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3062,6 +3106,12 @@
       <c r="BJ9" t="s">
         <v>36</v>
       </c>
+      <c r="BK9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3286,6 +3336,12 @@
       <c r="BJ10" t="s">
         <v>36</v>
       </c>
+      <c r="BK10" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3510,6 +3566,12 @@
       <c r="BJ11" t="s">
         <v>36</v>
       </c>
+      <c r="BK11" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3734,6 +3796,12 @@
       <c r="BJ12" t="s">
         <v>36</v>
       </c>
+      <c r="BK12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3958,6 +4026,12 @@
       <c r="BJ13" t="s">
         <v>36</v>
       </c>
+      <c r="BK13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4182,6 +4256,12 @@
       <c r="BJ14" t="s">
         <v>36</v>
       </c>
+      <c r="BK14" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4406,6 +4486,12 @@
       <c r="BJ15" t="s">
         <v>36</v>
       </c>
+      <c r="BK15" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4630,6 +4716,12 @@
       <c r="BJ16" t="s">
         <v>36</v>
       </c>
+      <c r="BK16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4854,6 +4946,12 @@
       <c r="BJ17" t="s">
         <v>36</v>
       </c>
+      <c r="BK17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5078,6 +5176,12 @@
       <c r="BJ18" t="s">
         <v>36</v>
       </c>
+      <c r="BK18" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5302,6 +5406,12 @@
       <c r="BJ19" t="s">
         <v>36</v>
       </c>
+      <c r="BK19" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5526,6 +5636,12 @@
       <c r="BJ20" t="s">
         <v>36</v>
       </c>
+      <c r="BK20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5750,6 +5866,12 @@
       <c r="BJ21" t="s">
         <v>36</v>
       </c>
+      <c r="BK21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5974,6 +6096,12 @@
       <c r="BJ22" t="s">
         <v>36</v>
       </c>
+      <c r="BK22" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6198,6 +6326,12 @@
       <c r="BJ23" t="s">
         <v>36</v>
       </c>
+      <c r="BK23" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6422,6 +6556,12 @@
       <c r="BJ24" t="s">
         <v>36</v>
       </c>
+      <c r="BK24" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6646,6 +6786,12 @@
       <c r="BJ25" t="s">
         <v>36</v>
       </c>
+      <c r="BK25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6870,6 +7016,12 @@
       <c r="BJ26" t="s">
         <v>36</v>
       </c>
+      <c r="BK26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7094,6 +7246,12 @@
       <c r="BJ27" t="s">
         <v>36</v>
       </c>
+      <c r="BK27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7318,6 +7476,12 @@
       <c r="BJ28" t="s">
         <v>36</v>
       </c>
+      <c r="BK28" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7542,6 +7706,12 @@
       <c r="BJ29" t="s">
         <v>36</v>
       </c>
+      <c r="BK29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7766,6 +7936,12 @@
       <c r="BJ30" t="s">
         <v>36</v>
       </c>
+      <c r="BK30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7990,6 +8166,12 @@
       <c r="BJ31" t="s">
         <v>36</v>
       </c>
+      <c r="BK31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8214,6 +8396,12 @@
       <c r="BJ32" t="s">
         <v>36</v>
       </c>
+      <c r="BK32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8436,6 +8624,12 @@
         <v>36</v>
       </c>
       <c r="BJ33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BK33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BL33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEF2BC2-3459-42A7-AD8B-06E1649DF71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5686F7-F9A7-4AA3-BBBF-4FE92E97BB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -1690,6 +1690,9 @@
       <c r="BL3" t="s">
         <v>36</v>
       </c>
+      <c r="BM3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -1934,6 +1937,9 @@
       <c r="BL4" t="s">
         <v>36</v>
       </c>
+      <c r="BM4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2178,6 +2184,9 @@
       <c r="BL5" t="s">
         <v>36</v>
       </c>
+      <c r="BM5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2422,6 +2431,9 @@
       <c r="BL6" t="s">
         <v>36</v>
       </c>
+      <c r="BM6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2652,6 +2664,9 @@
       <c r="BL7" t="s">
         <v>36</v>
       </c>
+      <c r="BM7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2882,6 +2897,9 @@
       <c r="BL8" t="s">
         <v>36</v>
       </c>
+      <c r="BM8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3112,6 +3130,9 @@
       <c r="BL9" t="s">
         <v>36</v>
       </c>
+      <c r="BM9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3342,6 +3363,9 @@
       <c r="BL10" t="s">
         <v>36</v>
       </c>
+      <c r="BM10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3572,6 +3596,9 @@
       <c r="BL11" t="s">
         <v>36</v>
       </c>
+      <c r="BM11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3802,6 +3829,9 @@
       <c r="BL12" t="s">
         <v>36</v>
       </c>
+      <c r="BM12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4032,6 +4062,9 @@
       <c r="BL13" t="s">
         <v>36</v>
       </c>
+      <c r="BM13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4262,6 +4295,9 @@
       <c r="BL14" t="s">
         <v>36</v>
       </c>
+      <c r="BM14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4492,6 +4528,9 @@
       <c r="BL15" t="s">
         <v>36</v>
       </c>
+      <c r="BM15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4722,6 +4761,9 @@
       <c r="BL16" t="s">
         <v>36</v>
       </c>
+      <c r="BM16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4952,6 +4994,9 @@
       <c r="BL17" t="s">
         <v>36</v>
       </c>
+      <c r="BM17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5182,6 +5227,9 @@
       <c r="BL18" t="s">
         <v>36</v>
       </c>
+      <c r="BM18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5412,6 +5460,9 @@
       <c r="BL19" t="s">
         <v>36</v>
       </c>
+      <c r="BM19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5642,6 +5693,9 @@
       <c r="BL20" t="s">
         <v>36</v>
       </c>
+      <c r="BM20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5872,6 +5926,9 @@
       <c r="BL21" t="s">
         <v>36</v>
       </c>
+      <c r="BM21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6102,6 +6159,9 @@
       <c r="BL22" t="s">
         <v>36</v>
       </c>
+      <c r="BM22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6332,6 +6392,9 @@
       <c r="BL23" t="s">
         <v>36</v>
       </c>
+      <c r="BM23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6562,6 +6625,9 @@
       <c r="BL24" t="s">
         <v>36</v>
       </c>
+      <c r="BM24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6792,6 +6858,9 @@
       <c r="BL25" t="s">
         <v>36</v>
       </c>
+      <c r="BM25" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7022,6 +7091,9 @@
       <c r="BL26" t="s">
         <v>36</v>
       </c>
+      <c r="BM26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7252,6 +7324,9 @@
       <c r="BL27" t="s">
         <v>36</v>
       </c>
+      <c r="BM27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7482,6 +7557,9 @@
       <c r="BL28" t="s">
         <v>36</v>
       </c>
+      <c r="BM28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7712,6 +7790,9 @@
       <c r="BL29" t="s">
         <v>36</v>
       </c>
+      <c r="BM29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7942,6 +8023,9 @@
       <c r="BL30" t="s">
         <v>36</v>
       </c>
+      <c r="BM30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8172,6 +8256,9 @@
       <c r="BL31" t="s">
         <v>36</v>
       </c>
+      <c r="BM31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8402,6 +8489,9 @@
       <c r="BL32" t="s">
         <v>36</v>
       </c>
+      <c r="BM32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8630,6 +8720,9 @@
         <v>36</v>
       </c>
       <c r="BL33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BM33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5686F7-F9A7-4AA3-BBBF-4FE92E97BB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEC50D1-323A-4C99-8DC2-C61D649C3F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>5F | P</t>
+  </si>
+  <si>
+    <t>P/7</t>
   </si>
 </sst>
 </file>
@@ -4296,7 +4299,7 @@
         <v>36</v>
       </c>
       <c r="BM14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEC50D1-323A-4C99-8DC2-C61D649C3F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC1A35-F9D9-4207-8A46-F71E4FF40830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1252,8 +1252,12 @@
       <c r="BM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BN1" s="1"/>
-      <c r="BO1" s="1"/>
+      <c r="BN1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -1473,8 +1477,12 @@
       <c r="BM2" s="1">
         <v>46297</v>
       </c>
-      <c r="BN2" s="1"/>
-      <c r="BO2" s="1"/>
+      <c r="BN2" s="1">
+        <v>46302</v>
+      </c>
+      <c r="BO2" s="1">
+        <v>46304</v>
+      </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="1"/>
@@ -1694,6 +1702,9 @@
         <v>36</v>
       </c>
       <c r="BM3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1943,6 +1954,9 @@
       <c r="BM4" t="s">
         <v>36</v>
       </c>
+      <c r="BN4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2190,6 +2204,9 @@
       <c r="BM5" t="s">
         <v>36</v>
       </c>
+      <c r="BN5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2437,6 +2454,9 @@
       <c r="BM6" t="s">
         <v>36</v>
       </c>
+      <c r="BN6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2670,6 +2690,9 @@
       <c r="BM7" t="s">
         <v>36</v>
       </c>
+      <c r="BN7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2903,6 +2926,9 @@
       <c r="BM8" t="s">
         <v>36</v>
       </c>
+      <c r="BN8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3136,6 +3162,9 @@
       <c r="BM9" t="s">
         <v>36</v>
       </c>
+      <c r="BN9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3369,6 +3398,9 @@
       <c r="BM10" t="s">
         <v>36</v>
       </c>
+      <c r="BN10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3602,6 +3634,9 @@
       <c r="BM11" t="s">
         <v>36</v>
       </c>
+      <c r="BN11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3835,6 +3870,9 @@
       <c r="BM12" t="s">
         <v>36</v>
       </c>
+      <c r="BN12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4068,6 +4106,9 @@
       <c r="BM13" t="s">
         <v>36</v>
       </c>
+      <c r="BN13" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4301,6 +4342,9 @@
       <c r="BM14" t="s">
         <v>47</v>
       </c>
+      <c r="BN14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4534,6 +4578,9 @@
       <c r="BM15" t="s">
         <v>36</v>
       </c>
+      <c r="BN15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4767,6 +4814,9 @@
       <c r="BM16" t="s">
         <v>36</v>
       </c>
+      <c r="BN16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5000,6 +5050,9 @@
       <c r="BM17" t="s">
         <v>36</v>
       </c>
+      <c r="BN17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5233,6 +5286,9 @@
       <c r="BM18" t="s">
         <v>36</v>
       </c>
+      <c r="BN18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5466,6 +5522,9 @@
       <c r="BM19" t="s">
         <v>36</v>
       </c>
+      <c r="BN19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5699,6 +5758,9 @@
       <c r="BM20" t="s">
         <v>36</v>
       </c>
+      <c r="BN20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5932,6 +5994,9 @@
       <c r="BM21" t="s">
         <v>36</v>
       </c>
+      <c r="BN21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6165,6 +6230,9 @@
       <c r="BM22" t="s">
         <v>36</v>
       </c>
+      <c r="BN22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6398,6 +6466,9 @@
       <c r="BM23" t="s">
         <v>36</v>
       </c>
+      <c r="BN23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6631,6 +6702,9 @@
       <c r="BM24" t="s">
         <v>36</v>
       </c>
+      <c r="BN24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6864,6 +6938,9 @@
       <c r="BM25" t="s">
         <v>37</v>
       </c>
+      <c r="BN25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7097,6 +7174,9 @@
       <c r="BM26" t="s">
         <v>36</v>
       </c>
+      <c r="BN26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7330,6 +7410,9 @@
       <c r="BM27" t="s">
         <v>36</v>
       </c>
+      <c r="BN27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7563,6 +7646,9 @@
       <c r="BM28" t="s">
         <v>36</v>
       </c>
+      <c r="BN28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7796,6 +7882,9 @@
       <c r="BM29" t="s">
         <v>36</v>
       </c>
+      <c r="BN29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8029,6 +8118,9 @@
       <c r="BM30" t="s">
         <v>36</v>
       </c>
+      <c r="BN30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8262,6 +8354,9 @@
       <c r="BM31" t="s">
         <v>36</v>
       </c>
+      <c r="BN31" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8495,6 +8590,9 @@
       <c r="BM32" t="s">
         <v>36</v>
       </c>
+      <c r="BN32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8726,6 +8824,9 @@
         <v>36</v>
       </c>
       <c r="BM33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FC1A35-F9D9-4207-8A46-F71E4FF40830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC505A-7634-40CE-89C3-4E9B99060434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1707,6 +1707,9 @@
       <c r="BN3" t="s">
         <v>36</v>
       </c>
+      <c r="BO3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -1957,6 +1960,9 @@
       <c r="BN4" t="s">
         <v>36</v>
       </c>
+      <c r="BO4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2207,6 +2213,9 @@
       <c r="BN5" t="s">
         <v>36</v>
       </c>
+      <c r="BO5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2457,6 +2466,9 @@
       <c r="BN6" t="s">
         <v>36</v>
       </c>
+      <c r="BO6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2693,6 +2705,9 @@
       <c r="BN7" t="s">
         <v>36</v>
       </c>
+      <c r="BO7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2929,6 +2944,9 @@
       <c r="BN8" t="s">
         <v>36</v>
       </c>
+      <c r="BO8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3165,6 +3183,9 @@
       <c r="BN9" t="s">
         <v>36</v>
       </c>
+      <c r="BO9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3401,6 +3422,9 @@
       <c r="BN10" t="s">
         <v>36</v>
       </c>
+      <c r="BO10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3637,6 +3661,9 @@
       <c r="BN11" t="s">
         <v>36</v>
       </c>
+      <c r="BO11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3873,6 +3900,9 @@
       <c r="BN12" t="s">
         <v>36</v>
       </c>
+      <c r="BO12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4109,6 +4139,9 @@
       <c r="BN13" t="s">
         <v>37</v>
       </c>
+      <c r="BO13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4345,6 +4378,9 @@
       <c r="BN14" t="s">
         <v>36</v>
       </c>
+      <c r="BO14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4581,6 +4617,9 @@
       <c r="BN15" t="s">
         <v>36</v>
       </c>
+      <c r="BO15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4817,6 +4856,9 @@
       <c r="BN16" t="s">
         <v>36</v>
       </c>
+      <c r="BO16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5053,6 +5095,9 @@
       <c r="BN17" t="s">
         <v>36</v>
       </c>
+      <c r="BO17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5289,6 +5334,9 @@
       <c r="BN18" t="s">
         <v>36</v>
       </c>
+      <c r="BO18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5525,6 +5573,9 @@
       <c r="BN19" t="s">
         <v>36</v>
       </c>
+      <c r="BO19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5761,6 +5812,9 @@
       <c r="BN20" t="s">
         <v>36</v>
       </c>
+      <c r="BO20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5997,6 +6051,9 @@
       <c r="BN21" t="s">
         <v>36</v>
       </c>
+      <c r="BO21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6233,6 +6290,9 @@
       <c r="BN22" t="s">
         <v>36</v>
       </c>
+      <c r="BO22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6469,6 +6529,9 @@
       <c r="BN23" t="s">
         <v>36</v>
       </c>
+      <c r="BO23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6705,6 +6768,9 @@
       <c r="BN24" t="s">
         <v>36</v>
       </c>
+      <c r="BO24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6941,6 +7007,9 @@
       <c r="BN25" t="s">
         <v>36</v>
       </c>
+      <c r="BO25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7177,6 +7246,9 @@
       <c r="BN26" t="s">
         <v>36</v>
       </c>
+      <c r="BO26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7413,6 +7485,9 @@
       <c r="BN27" t="s">
         <v>36</v>
       </c>
+      <c r="BO27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7649,6 +7724,9 @@
       <c r="BN28" t="s">
         <v>36</v>
       </c>
+      <c r="BO28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7885,6 +7963,9 @@
       <c r="BN29" t="s">
         <v>36</v>
       </c>
+      <c r="BO29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8121,6 +8202,9 @@
       <c r="BN30" t="s">
         <v>36</v>
       </c>
+      <c r="BO30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8357,6 +8441,9 @@
       <c r="BN31" t="s">
         <v>37</v>
       </c>
+      <c r="BO31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8593,6 +8680,9 @@
       <c r="BN32" t="s">
         <v>36</v>
       </c>
+      <c r="BO32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8827,6 +8917,9 @@
         <v>36</v>
       </c>
       <c r="BN33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BO33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC505A-7634-40CE-89C3-4E9B99060434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A35CF7-C0D4-4E80-A304-A398F695A5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1258,8 +1258,12 @@
       <c r="BO1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BP1" s="1"/>
-      <c r="BQ1" s="1"/>
+      <c r="BP1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
       <c r="BT1" s="2"/>
@@ -1483,8 +1487,12 @@
       <c r="BO2" s="1">
         <v>46304</v>
       </c>
-      <c r="BP2" s="1"/>
-      <c r="BQ2" s="1"/>
+      <c r="BP2" s="1">
+        <v>46309</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>46311</v>
+      </c>
       <c r="BR2" s="1"/>
       <c r="BS2" s="1"/>
       <c r="BT2" s="3"/>
@@ -1708,6 +1716,9 @@
         <v>36</v>
       </c>
       <c r="BO3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BP3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1963,6 +1974,9 @@
       <c r="BO4" t="s">
         <v>36</v>
       </c>
+      <c r="BP4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2216,6 +2230,9 @@
       <c r="BO5" t="s">
         <v>36</v>
       </c>
+      <c r="BP5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2469,6 +2486,9 @@
       <c r="BO6" t="s">
         <v>36</v>
       </c>
+      <c r="BP6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2708,6 +2728,9 @@
       <c r="BO7" t="s">
         <v>36</v>
       </c>
+      <c r="BP7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2947,6 +2970,9 @@
       <c r="BO8" t="s">
         <v>36</v>
       </c>
+      <c r="BP8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3186,6 +3212,9 @@
       <c r="BO9" t="s">
         <v>36</v>
       </c>
+      <c r="BP9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3425,6 +3454,9 @@
       <c r="BO10" t="s">
         <v>36</v>
       </c>
+      <c r="BP10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3664,6 +3696,9 @@
       <c r="BO11" t="s">
         <v>36</v>
       </c>
+      <c r="BP11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3903,6 +3938,9 @@
       <c r="BO12" t="s">
         <v>36</v>
       </c>
+      <c r="BP12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4142,6 +4180,9 @@
       <c r="BO13" t="s">
         <v>36</v>
       </c>
+      <c r="BP13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4381,6 +4422,9 @@
       <c r="BO14" t="s">
         <v>36</v>
       </c>
+      <c r="BP14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4620,6 +4664,9 @@
       <c r="BO15" t="s">
         <v>36</v>
       </c>
+      <c r="BP15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4859,6 +4906,9 @@
       <c r="BO16" t="s">
         <v>36</v>
       </c>
+      <c r="BP16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5098,6 +5148,9 @@
       <c r="BO17" t="s">
         <v>36</v>
       </c>
+      <c r="BP17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5337,6 +5390,9 @@
       <c r="BO18" t="s">
         <v>36</v>
       </c>
+      <c r="BP18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5576,6 +5632,9 @@
       <c r="BO19" t="s">
         <v>36</v>
       </c>
+      <c r="BP19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5815,6 +5874,9 @@
       <c r="BO20" t="s">
         <v>36</v>
       </c>
+      <c r="BP20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6054,6 +6116,9 @@
       <c r="BO21" t="s">
         <v>36</v>
       </c>
+      <c r="BP21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6293,6 +6358,9 @@
       <c r="BO22" t="s">
         <v>36</v>
       </c>
+      <c r="BP22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6532,6 +6600,9 @@
       <c r="BO23" t="s">
         <v>36</v>
       </c>
+      <c r="BP23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6771,6 +6842,9 @@
       <c r="BO24" t="s">
         <v>36</v>
       </c>
+      <c r="BP24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7010,6 +7084,9 @@
       <c r="BO25" t="s">
         <v>36</v>
       </c>
+      <c r="BP25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7249,6 +7326,9 @@
       <c r="BO26" t="s">
         <v>36</v>
       </c>
+      <c r="BP26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7488,6 +7568,9 @@
       <c r="BO27" t="s">
         <v>36</v>
       </c>
+      <c r="BP27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7727,6 +7810,9 @@
       <c r="BO28" t="s">
         <v>36</v>
       </c>
+      <c r="BP28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7966,6 +8052,9 @@
       <c r="BO29" t="s">
         <v>36</v>
       </c>
+      <c r="BP29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8205,6 +8294,9 @@
       <c r="BO30" t="s">
         <v>36</v>
       </c>
+      <c r="BP30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8444,6 +8536,9 @@
       <c r="BO31" t="s">
         <v>36</v>
       </c>
+      <c r="BP31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8683,6 +8778,9 @@
       <c r="BO32" t="s">
         <v>36</v>
       </c>
+      <c r="BP32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -8920,6 +9018,9 @@
         <v>36</v>
       </c>
       <c r="BO33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BP33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A35CF7-C0D4-4E80-A304-A398F695A5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F950346-9C34-4465-8784-C6978B91691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1721,6 +1721,9 @@
       <c r="BP3" t="s">
         <v>36</v>
       </c>
+      <c r="BQ3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -1977,6 +1980,9 @@
       <c r="BP4" t="s">
         <v>36</v>
       </c>
+      <c r="BQ4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2233,6 +2239,9 @@
       <c r="BP5" t="s">
         <v>36</v>
       </c>
+      <c r="BQ5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2489,6 +2498,9 @@
       <c r="BP6" t="s">
         <v>36</v>
       </c>
+      <c r="BQ6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2731,6 +2743,9 @@
       <c r="BP7" t="s">
         <v>36</v>
       </c>
+      <c r="BQ7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2973,6 +2988,9 @@
       <c r="BP8" t="s">
         <v>36</v>
       </c>
+      <c r="BQ8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3215,6 +3233,9 @@
       <c r="BP9" t="s">
         <v>36</v>
       </c>
+      <c r="BQ9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3457,6 +3478,9 @@
       <c r="BP10" t="s">
         <v>36</v>
       </c>
+      <c r="BQ10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3699,6 +3723,9 @@
       <c r="BP11" t="s">
         <v>36</v>
       </c>
+      <c r="BQ11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3941,6 +3968,9 @@
       <c r="BP12" t="s">
         <v>36</v>
       </c>
+      <c r="BQ12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4183,6 +4213,9 @@
       <c r="BP13" t="s">
         <v>36</v>
       </c>
+      <c r="BQ13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4425,6 +4458,9 @@
       <c r="BP14" t="s">
         <v>36</v>
       </c>
+      <c r="BQ14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4667,6 +4703,9 @@
       <c r="BP15" t="s">
         <v>36</v>
       </c>
+      <c r="BQ15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4909,6 +4948,9 @@
       <c r="BP16" t="s">
         <v>36</v>
       </c>
+      <c r="BQ16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5151,6 +5193,9 @@
       <c r="BP17" t="s">
         <v>36</v>
       </c>
+      <c r="BQ17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5393,6 +5438,9 @@
       <c r="BP18" t="s">
         <v>36</v>
       </c>
+      <c r="BQ18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5635,6 +5683,9 @@
       <c r="BP19" t="s">
         <v>36</v>
       </c>
+      <c r="BQ19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5877,6 +5928,9 @@
       <c r="BP20" t="s">
         <v>36</v>
       </c>
+      <c r="BQ20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6119,6 +6173,9 @@
       <c r="BP21" t="s">
         <v>36</v>
       </c>
+      <c r="BQ21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6361,6 +6418,9 @@
       <c r="BP22" t="s">
         <v>36</v>
       </c>
+      <c r="BQ22" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6603,6 +6663,9 @@
       <c r="BP23" t="s">
         <v>36</v>
       </c>
+      <c r="BQ23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6845,6 +6908,9 @@
       <c r="BP24" t="s">
         <v>36</v>
       </c>
+      <c r="BQ24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7087,6 +7153,9 @@
       <c r="BP25" t="s">
         <v>36</v>
       </c>
+      <c r="BQ25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7329,6 +7398,9 @@
       <c r="BP26" t="s">
         <v>36</v>
       </c>
+      <c r="BQ26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7571,6 +7643,9 @@
       <c r="BP27" t="s">
         <v>36</v>
       </c>
+      <c r="BQ27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7813,6 +7888,9 @@
       <c r="BP28" t="s">
         <v>36</v>
       </c>
+      <c r="BQ28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -8055,6 +8133,9 @@
       <c r="BP29" t="s">
         <v>36</v>
       </c>
+      <c r="BQ29" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8297,6 +8378,9 @@
       <c r="BP30" t="s">
         <v>36</v>
       </c>
+      <c r="BQ30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8539,6 +8623,9 @@
       <c r="BP31" t="s">
         <v>36</v>
       </c>
+      <c r="BQ31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8781,6 +8868,9 @@
       <c r="BP32" t="s">
         <v>36</v>
       </c>
+      <c r="BQ32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -9021,6 +9111,9 @@
         <v>36</v>
       </c>
       <c r="BP33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BQ33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F950346-9C34-4465-8784-C6978B91691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA391F33-6224-4DC2-A5D7-E7CBD6D38027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1264,8 +1264,12 @@
       <c r="BQ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
+      <c r="BR1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
@@ -1493,8 +1497,12 @@
       <c r="BQ2" s="1">
         <v>46311</v>
       </c>
-      <c r="BR2" s="1"/>
-      <c r="BS2" s="1"/>
+      <c r="BR2" s="1">
+        <v>46316</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>46317</v>
+      </c>
       <c r="BT2" s="3"/>
       <c r="BU2" s="3"/>
       <c r="BV2" s="3"/>
@@ -1722,6 +1730,9 @@
         <v>36</v>
       </c>
       <c r="BQ3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1983,6 +1994,9 @@
       <c r="BQ4" t="s">
         <v>36</v>
       </c>
+      <c r="BR4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2242,6 +2256,9 @@
       <c r="BQ5" t="s">
         <v>36</v>
       </c>
+      <c r="BR5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2501,6 +2518,9 @@
       <c r="BQ6" t="s">
         <v>36</v>
       </c>
+      <c r="BR6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2746,6 +2766,9 @@
       <c r="BQ7" t="s">
         <v>36</v>
       </c>
+      <c r="BR7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2991,6 +3014,9 @@
       <c r="BQ8" t="s">
         <v>36</v>
       </c>
+      <c r="BR8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3236,6 +3262,9 @@
       <c r="BQ9" t="s">
         <v>36</v>
       </c>
+      <c r="BR9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3481,6 +3510,9 @@
       <c r="BQ10" t="s">
         <v>36</v>
       </c>
+      <c r="BR10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3726,6 +3758,9 @@
       <c r="BQ11" t="s">
         <v>36</v>
       </c>
+      <c r="BR11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3971,6 +4006,9 @@
       <c r="BQ12" t="s">
         <v>36</v>
       </c>
+      <c r="BR12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4216,6 +4254,9 @@
       <c r="BQ13" t="s">
         <v>36</v>
       </c>
+      <c r="BR13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4461,6 +4502,9 @@
       <c r="BQ14" t="s">
         <v>36</v>
       </c>
+      <c r="BR14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4706,6 +4750,9 @@
       <c r="BQ15" t="s">
         <v>36</v>
       </c>
+      <c r="BR15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4951,6 +4998,9 @@
       <c r="BQ16" t="s">
         <v>36</v>
       </c>
+      <c r="BR16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5196,6 +5246,9 @@
       <c r="BQ17" t="s">
         <v>36</v>
       </c>
+      <c r="BR17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5441,6 +5494,9 @@
       <c r="BQ18" t="s">
         <v>36</v>
       </c>
+      <c r="BR18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5686,6 +5742,9 @@
       <c r="BQ19" t="s">
         <v>36</v>
       </c>
+      <c r="BR19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5931,6 +5990,9 @@
       <c r="BQ20" t="s">
         <v>36</v>
       </c>
+      <c r="BR20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6176,6 +6238,9 @@
       <c r="BQ21" t="s">
         <v>36</v>
       </c>
+      <c r="BR21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6421,6 +6486,9 @@
       <c r="BQ22" t="s">
         <v>37</v>
       </c>
+      <c r="BR22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6666,6 +6734,9 @@
       <c r="BQ23" t="s">
         <v>36</v>
       </c>
+      <c r="BR23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6911,6 +6982,9 @@
       <c r="BQ24" t="s">
         <v>36</v>
       </c>
+      <c r="BR24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7156,6 +7230,9 @@
       <c r="BQ25" t="s">
         <v>36</v>
       </c>
+      <c r="BR25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7401,6 +7478,9 @@
       <c r="BQ26" t="s">
         <v>36</v>
       </c>
+      <c r="BR26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7646,6 +7726,9 @@
       <c r="BQ27" t="s">
         <v>36</v>
       </c>
+      <c r="BR27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7891,6 +7974,9 @@
       <c r="BQ28" t="s">
         <v>36</v>
       </c>
+      <c r="BR28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -8136,6 +8222,9 @@
       <c r="BQ29" t="s">
         <v>37</v>
       </c>
+      <c r="BR29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8381,6 +8470,9 @@
       <c r="BQ30" t="s">
         <v>36</v>
       </c>
+      <c r="BR30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8626,6 +8718,9 @@
       <c r="BQ31" t="s">
         <v>36</v>
       </c>
+      <c r="BR31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8871,6 +8966,9 @@
       <c r="BQ32" t="s">
         <v>36</v>
       </c>
+      <c r="BR32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -9114,6 +9212,9 @@
         <v>36</v>
       </c>
       <c r="BQ33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA391F33-6224-4DC2-A5D7-E7CBD6D38027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C379D5-41E9-4CAB-8958-B81CE644CB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1501,7 +1501,7 @@
         <v>46316</v>
       </c>
       <c r="BS2" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="BT2" s="3"/>
       <c r="BU2" s="3"/>
@@ -1733,6 +1733,9 @@
         <v>36</v>
       </c>
       <c r="BR3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1997,6 +2000,9 @@
       <c r="BR4" t="s">
         <v>36</v>
       </c>
+      <c r="BS4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2259,6 +2265,9 @@
       <c r="BR5" t="s">
         <v>36</v>
       </c>
+      <c r="BS5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2521,6 +2530,9 @@
       <c r="BR6" t="s">
         <v>36</v>
       </c>
+      <c r="BS6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2769,6 +2781,9 @@
       <c r="BR7" t="s">
         <v>36</v>
       </c>
+      <c r="BS7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -3017,6 +3032,9 @@
       <c r="BR8" t="s">
         <v>36</v>
       </c>
+      <c r="BS8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3265,6 +3283,9 @@
       <c r="BR9" t="s">
         <v>36</v>
       </c>
+      <c r="BS9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3513,6 +3534,9 @@
       <c r="BR10" t="s">
         <v>36</v>
       </c>
+      <c r="BS10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3761,6 +3785,9 @@
       <c r="BR11" t="s">
         <v>36</v>
       </c>
+      <c r="BS11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -4009,6 +4036,9 @@
       <c r="BR12" t="s">
         <v>36</v>
       </c>
+      <c r="BS12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4257,6 +4287,9 @@
       <c r="BR13" t="s">
         <v>36</v>
       </c>
+      <c r="BS13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4505,6 +4538,9 @@
       <c r="BR14" t="s">
         <v>36</v>
       </c>
+      <c r="BS14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4753,6 +4789,9 @@
       <c r="BR15" t="s">
         <v>36</v>
       </c>
+      <c r="BS15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -5001,6 +5040,9 @@
       <c r="BR16" t="s">
         <v>36</v>
       </c>
+      <c r="BS16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5249,6 +5291,9 @@
       <c r="BR17" t="s">
         <v>36</v>
       </c>
+      <c r="BS17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5497,6 +5542,9 @@
       <c r="BR18" t="s">
         <v>36</v>
       </c>
+      <c r="BS18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5745,6 +5793,9 @@
       <c r="BR19" t="s">
         <v>36</v>
       </c>
+      <c r="BS19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5993,6 +6044,9 @@
       <c r="BR20" t="s">
         <v>36</v>
       </c>
+      <c r="BS20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6241,6 +6295,9 @@
       <c r="BR21" t="s">
         <v>36</v>
       </c>
+      <c r="BS21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6489,6 +6546,9 @@
       <c r="BR22" t="s">
         <v>36</v>
       </c>
+      <c r="BS22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6737,6 +6797,9 @@
       <c r="BR23" t="s">
         <v>36</v>
       </c>
+      <c r="BS23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6985,6 +7048,9 @@
       <c r="BR24" t="s">
         <v>36</v>
       </c>
+      <c r="BS24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7233,6 +7299,9 @@
       <c r="BR25" t="s">
         <v>36</v>
       </c>
+      <c r="BS25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7481,6 +7550,9 @@
       <c r="BR26" t="s">
         <v>36</v>
       </c>
+      <c r="BS26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7729,6 +7801,9 @@
       <c r="BR27" t="s">
         <v>36</v>
       </c>
+      <c r="BS27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -7977,6 +8052,9 @@
       <c r="BR28" t="s">
         <v>36</v>
       </c>
+      <c r="BS28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -8225,6 +8303,9 @@
       <c r="BR29" t="s">
         <v>36</v>
       </c>
+      <c r="BS29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8473,6 +8554,9 @@
       <c r="BR30" t="s">
         <v>36</v>
       </c>
+      <c r="BS30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8721,6 +8805,9 @@
       <c r="BR31" t="s">
         <v>36</v>
       </c>
+      <c r="BS31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -8969,6 +9056,9 @@
       <c r="BR32" t="s">
         <v>36</v>
       </c>
+      <c r="BS32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -9215,6 +9305,9 @@
         <v>36</v>
       </c>
       <c r="BR33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C379D5-41E9-4CAB-8958-B81CE644CB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE848DC9-09C4-4D5E-8693-DA271F10CC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2531,7 +2531,7 @@
         <v>36</v>
       </c>
       <c r="BS6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE848DC9-09C4-4D5E-8693-DA271F10CC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D45E785-A49C-4ED3-8C97-A99D21850ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1270,8 +1270,12 @@
       <c r="BS1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
+      <c r="BT1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="BU1" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="BV1" s="2"/>
       <c r="BW1" s="2"/>
       <c r="BX1" s="2"/>
@@ -1503,8 +1507,12 @@
       <c r="BS2" s="1">
         <v>46318</v>
       </c>
-      <c r="BT2" s="3"/>
-      <c r="BU2" s="3"/>
+      <c r="BT2" s="1">
+        <v>46323</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>46325</v>
+      </c>
       <c r="BV2" s="3"/>
       <c r="BW2" s="3"/>
       <c r="BX2" s="3"/>
@@ -1736,6 +1744,9 @@
         <v>36</v>
       </c>
       <c r="BS3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BT3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -2003,6 +2014,9 @@
       <c r="BS4" t="s">
         <v>36</v>
       </c>
+      <c r="BT4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2268,6 +2282,9 @@
       <c r="BS5" t="s">
         <v>36</v>
       </c>
+      <c r="BT5" t="s">
+        <v>37</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2533,6 +2550,9 @@
       <c r="BS6" t="s">
         <v>38</v>
       </c>
+      <c r="BT6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2784,6 +2804,9 @@
       <c r="BS7" t="s">
         <v>36</v>
       </c>
+      <c r="BT7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -3035,6 +3058,9 @@
       <c r="BS8" t="s">
         <v>36</v>
       </c>
+      <c r="BT8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3286,6 +3312,9 @@
       <c r="BS9" t="s">
         <v>36</v>
       </c>
+      <c r="BT9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3537,6 +3566,9 @@
       <c r="BS10" t="s">
         <v>36</v>
       </c>
+      <c r="BT10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3788,6 +3820,9 @@
       <c r="BS11" t="s">
         <v>36</v>
       </c>
+      <c r="BT11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -4039,6 +4074,9 @@
       <c r="BS12" t="s">
         <v>36</v>
       </c>
+      <c r="BT12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4290,6 +4328,9 @@
       <c r="BS13" t="s">
         <v>36</v>
       </c>
+      <c r="BT13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4541,6 +4582,9 @@
       <c r="BS14" t="s">
         <v>36</v>
       </c>
+      <c r="BT14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4792,6 +4836,9 @@
       <c r="BS15" t="s">
         <v>36</v>
       </c>
+      <c r="BT15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -5043,6 +5090,9 @@
       <c r="BS16" t="s">
         <v>36</v>
       </c>
+      <c r="BT16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5294,6 +5344,9 @@
       <c r="BS17" t="s">
         <v>36</v>
       </c>
+      <c r="BT17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5545,6 +5598,9 @@
       <c r="BS18" t="s">
         <v>36</v>
       </c>
+      <c r="BT18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5796,6 +5852,9 @@
       <c r="BS19" t="s">
         <v>36</v>
       </c>
+      <c r="BT19" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -6047,6 +6106,9 @@
       <c r="BS20" t="s">
         <v>36</v>
       </c>
+      <c r="BT20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6298,6 +6360,9 @@
       <c r="BS21" t="s">
         <v>36</v>
       </c>
+      <c r="BT21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6549,6 +6614,9 @@
       <c r="BS22" t="s">
         <v>36</v>
       </c>
+      <c r="BT22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6800,6 +6868,9 @@
       <c r="BS23" t="s">
         <v>36</v>
       </c>
+      <c r="BT23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -7051,6 +7122,9 @@
       <c r="BS24" t="s">
         <v>36</v>
       </c>
+      <c r="BT24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7302,6 +7376,9 @@
       <c r="BS25" t="s">
         <v>36</v>
       </c>
+      <c r="BT25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7553,6 +7630,9 @@
       <c r="BS26" t="s">
         <v>36</v>
       </c>
+      <c r="BT26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7804,6 +7884,9 @@
       <c r="BS27" t="s">
         <v>36</v>
       </c>
+      <c r="BT27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -8055,6 +8138,9 @@
       <c r="BS28" t="s">
         <v>36</v>
       </c>
+      <c r="BT28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -8306,6 +8392,9 @@
       <c r="BS29" t="s">
         <v>36</v>
       </c>
+      <c r="BT29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8557,6 +8646,9 @@
       <c r="BS30" t="s">
         <v>36</v>
       </c>
+      <c r="BT30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8808,6 +8900,9 @@
       <c r="BS31" t="s">
         <v>36</v>
       </c>
+      <c r="BT31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -9059,6 +9154,9 @@
       <c r="BS32" t="s">
         <v>36</v>
       </c>
+      <c r="BT32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -9308,6 +9406,9 @@
         <v>36</v>
       </c>
       <c r="BS33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BT33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D45E785-A49C-4ED3-8C97-A99D21850ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3F0160-164D-47AC-8E4D-763077451CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -1749,6 +1749,9 @@
       <c r="BT3" t="s">
         <v>36</v>
       </c>
+      <c r="BU3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -2017,6 +2020,9 @@
       <c r="BT4" t="s">
         <v>36</v>
       </c>
+      <c r="BU4" t="s">
+        <v>37</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2285,6 +2291,9 @@
       <c r="BT5" t="s">
         <v>37</v>
       </c>
+      <c r="BU5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2553,6 +2562,9 @@
       <c r="BT6" t="s">
         <v>36</v>
       </c>
+      <c r="BU6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2807,6 +2819,9 @@
       <c r="BT7" t="s">
         <v>36</v>
       </c>
+      <c r="BU7" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -3061,6 +3076,9 @@
       <c r="BT8" t="s">
         <v>36</v>
       </c>
+      <c r="BU8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -3315,6 +3333,9 @@
       <c r="BT9" t="s">
         <v>36</v>
       </c>
+      <c r="BU9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3569,6 +3590,9 @@
       <c r="BT10" t="s">
         <v>36</v>
       </c>
+      <c r="BU10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3823,6 +3847,9 @@
       <c r="BT11" t="s">
         <v>36</v>
       </c>
+      <c r="BU11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -4077,6 +4104,9 @@
       <c r="BT12" t="s">
         <v>36</v>
       </c>
+      <c r="BU12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -4331,6 +4361,9 @@
       <c r="BT13" t="s">
         <v>36</v>
       </c>
+      <c r="BU13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -4585,6 +4618,9 @@
       <c r="BT14" t="s">
         <v>36</v>
       </c>
+      <c r="BU14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4839,6 +4875,9 @@
       <c r="BT15" t="s">
         <v>36</v>
       </c>
+      <c r="BU15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -5093,6 +5132,9 @@
       <c r="BT16" t="s">
         <v>36</v>
       </c>
+      <c r="BU16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -5347,6 +5389,9 @@
       <c r="BT17" t="s">
         <v>36</v>
       </c>
+      <c r="BU17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -5601,6 +5646,9 @@
       <c r="BT18" t="s">
         <v>36</v>
       </c>
+      <c r="BU18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5855,6 +5903,9 @@
       <c r="BT19" t="s">
         <v>37</v>
       </c>
+      <c r="BU19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -6109,6 +6160,9 @@
       <c r="BT20" t="s">
         <v>36</v>
       </c>
+      <c r="BU20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -6363,6 +6417,9 @@
       <c r="BT21" t="s">
         <v>36</v>
       </c>
+      <c r="BU21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -6617,6 +6674,9 @@
       <c r="BT22" t="s">
         <v>36</v>
       </c>
+      <c r="BU22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -6871,6 +6931,9 @@
       <c r="BT23" t="s">
         <v>36</v>
       </c>
+      <c r="BU23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -7125,6 +7188,9 @@
       <c r="BT24" t="s">
         <v>36</v>
       </c>
+      <c r="BU24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -7379,6 +7445,9 @@
       <c r="BT25" t="s">
         <v>36</v>
       </c>
+      <c r="BU25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -7633,6 +7702,9 @@
       <c r="BT26" t="s">
         <v>36</v>
       </c>
+      <c r="BU26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -7887,6 +7959,9 @@
       <c r="BT27" t="s">
         <v>36</v>
       </c>
+      <c r="BU27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -8141,6 +8216,9 @@
       <c r="BT28" t="s">
         <v>36</v>
       </c>
+      <c r="BU28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -8395,6 +8473,9 @@
       <c r="BT29" t="s">
         <v>36</v>
       </c>
+      <c r="BU29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -8649,6 +8730,9 @@
       <c r="BT30" t="s">
         <v>36</v>
       </c>
+      <c r="BU30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -8903,6 +8987,9 @@
       <c r="BT31" t="s">
         <v>36</v>
       </c>
+      <c r="BU31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -9157,6 +9244,9 @@
       <c r="BT32" t="s">
         <v>36</v>
       </c>
+      <c r="BU32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -9409,6 +9499,9 @@
         <v>36</v>
       </c>
       <c r="BT33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BU33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3F0160-164D-47AC-8E4D-763077451CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0609F3A-4AC3-4232-B34E-70ACE46AC46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4105,7 +4105,7 @@
         <v>36</v>
       </c>
       <c r="BU12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
